--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,22 +2049,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>St Etienne x Grenoble</t>
+          <t>Al Ahli x Abha</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="K21" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="L21" t="n">
-        <v>22.73</v>
+        <v>14.71</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -2123,27 +2123,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al Ahli x Abha</t>
+          <t>PFC Levski Sofia x Spartak Varna</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2162,20 +2162,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="K22" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="L22" t="n">
-        <v>14.71</v>
+        <v>19.23</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2202,27 +2202,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia x Spartak Varna</t>
+          <t>Olympiakos x Atromitos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2241,20 +2241,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="L23" t="n">
-        <v>19.23</v>
+        <v>16.67</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2286,22 +2286,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Olympiakos x Atromitos</t>
+          <t>Fenerbahce x Konyaspor</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2320,20 +2320,20 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="K24" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="L24" t="n">
-        <v>16.67</v>
+        <v>17.86</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2360,37 +2360,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fenerbahce x Konyaspor</t>
+          <t>Toulouse x Lyon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2399,20 +2399,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>17.86</v>
+        <v>6.67</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2439,27 +2439,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FRANCE 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Toulouse x Lyon</t>
+          <t>Benevento x Modena</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2478,20 +2478,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>6.67</v>
+        <v>6.45</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2523,32 +2523,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Benevento x Modena</t>
+          <t>Univ Catolica (Ecu) x Manta FC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2557,20 +2557,20 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L27" t="n">
-        <v>6.45</v>
+        <v>19.23</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2597,27 +2597,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu) x Manta FC</t>
+          <t>Sporting Lisbon x Alverca</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2636,20 +2636,20 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="L28" t="n">
-        <v>19.23</v>
+        <v>13.89</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2681,32 +2681,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sporting Lisbon x Alverca</t>
+          <t>Espanyol x Real Madrid</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2715,20 +2715,20 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K29" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="L29" t="n">
-        <v>13.89</v>
+        <v>13.16</v>
       </c>
       <c r="M29" t="n">
         <v>100</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Espanyol x Real Madrid</t>
+          <t>Rayo Zuliano x Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2794,20 +2794,20 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="K30" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="L30" t="n">
-        <v>13.16</v>
+        <v>16.67</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2834,37 +2834,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rayo Zuliano x Deportivo La Guaira</t>
+          <t>Inter Miami CF x Toronto FC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Toronto FC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2873,20 +2873,20 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="K31" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="L31" t="n">
-        <v>16.67</v>
+        <v>17.86</v>
       </c>
       <c r="M31" t="n">
         <v>100</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,27 +2913,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Inter Miami CF x Toronto FC</t>
+          <t>Ind Medellin x Cucuta Deportivo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Ind Medellin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2952,20 +2952,20 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="L32" t="n">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="M32" t="n">
         <v>100</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2992,27 +2992,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ind Medellin x Cucuta Deportivo</t>
+          <t>Vancouver Whitecaps x FC Dallas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3031,20 +3031,20 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="K33" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="L33" t="n">
-        <v>17.24</v>
+        <v>20.83</v>
       </c>
       <c r="M33" t="n">
         <v>100</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3071,37 +3071,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps x FC Dallas</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>FC Dallas</t>
-        </is>
-      </c>
+          <t>Levski Sofia x Spartak Varna</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3110,37 +3102,43 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="L34" t="n">
-        <v>20.83</v>
+        <v>7.69</v>
       </c>
       <c r="M34" t="n">
         <v>100</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3150,17 +3148,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Levski Sofia x Spartak Varna</t>
+          <t>St Etienne x Grenoble</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3181,20 +3179,20 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="K35" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L35" t="n">
-        <v>7.69</v>
+        <v>9.52</v>
       </c>
       <c r="M35" t="n">
         <v>100</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3208,89 +3206,12 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>7.42</v>
+        <v>9.19</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FRANCE 2</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>St Etienne x Grenoble</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Match Odds (Away)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L36" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="M36" t="n">
-        <v>100</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>4x0</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -543,37 +553,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAPAN 2</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yamagata x Yokohama FC</t>
+          <t>Okayama x Tokyo-V</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yamagata</t>
+          <t>Okayama</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yokohama FC</t>
+          <t>Tokyo-V</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -582,20 +592,20 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4.55</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -610,9 +620,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>9.65</v>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,27 +640,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 1</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Anyang x FC Seoul</t>
+          <t>Yamagata x Yokohama FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Anyang</t>
+          <t>Yamagata</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Yokohama FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -661,20 +679,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x7</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -692,6 +710,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,32 +726,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SOUTH KOREA 2</t>
+          <t>SOUTH KOREA 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cheonan City x Suwon Bluewings</t>
+          <t>FC Anyang x FC Seoul</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>FC Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -740,20 +760,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18.52</v>
+        <v>4.76</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0x7</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -771,6 +791,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,27 +802,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>SOUTH KOREA 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka x Guangdong GZ-Power FC</t>
+          <t>Cheonan City x Suwon Bluewings</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangdong GZ-Power FC</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -819,20 +841,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="L5" t="n">
-        <v>13.89</v>
+        <v>18.52</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x5</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,6 +872,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -864,32 +888,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hull x Man Utd</t>
+          <t>Meizhou Hakka x Guangdong GZ-Power FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hull</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Guangdong GZ-Power FC</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +922,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="L6" t="n">
-        <v>21.28</v>
+        <v>13.89</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x5</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +953,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,37 +964,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHINA 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beijing Guoan x Yunnan Yukun</t>
+          <t>Hull x Man Utd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Hull</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,20 +1003,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16.5</v>
+        <v>5.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="L7" t="n">
-        <v>6.45</v>
+        <v>21.28</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3x3</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1008,6 +1034,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1045,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NETHERLANDS 2</t>
+          <t>CHINA 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NAC Breda x Jong Ajax Amsterdam</t>
+          <t>Beijing Guoan x Yunnan Yukun</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,20 +1084,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.13</v>
+        <v>6.45</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3x3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1087,6 +1115,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1101,32 +1131,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fortuna Sittard x AZ Alkmaar</t>
+          <t>NAC Breda x Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,20 +1165,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="L9" t="n">
-        <v>21.28</v>
+        <v>16.13</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1166,6 +1196,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1207,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SK Artis Brno x Sparta Prague</t>
+          <t>Fortuna Sittard x AZ Alkmaar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1246,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="L10" t="n">
-        <v>20.83</v>
+        <v>21.28</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1277,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1279,12 +1313,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,13 +1327,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="K11" t="n">
         <v>1.4</v>
       </c>
       <c r="L11" t="n">
-        <v>11.9</v>
+        <v>20.83</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -1324,6 +1358,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,37 +1369,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ludogorets x Slavia Sofia</t>
+          <t>SK Artis Brno x Sparta Prague</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1372,20 +1408,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="L12" t="n">
-        <v>22.22</v>
+        <v>11.9</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1403,6 +1439,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,37 +1450,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ESTONIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Harju JK Laagri x Nomme Kalju</t>
+          <t>Oviedo x Leganes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1489,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>21.74</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1479,9 +1517,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>9.65</v>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1496,32 +1542,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Guidonia Montecelio 1937 x Gubbio</t>
+          <t>Ludogorets x Slavia Sofia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Guidonia Montecelio 1937</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1530,20 +1576,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="L14" t="n">
-        <v>5.88</v>
+        <v>22.22</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1561,6 +1607,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1575,32 +1623,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>ESTONIA 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sport Huancayo x Cesar Vallejo Moquegua</t>
+          <t>Harju JK Laagri x Nomme Kalju</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Huancayo</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cesar Vallejo Moquegua</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1609,20 +1657,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K15" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="L15" t="n">
-        <v>21.28</v>
+        <v>21.74</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1640,6 +1688,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1649,37 +1699,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>ITALY 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Udinese x Como</t>
+          <t>FC Guidonia Montecelio 1937 x Gubbio</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>FC Guidonia Montecelio 1937</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1688,20 +1738,20 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="L16" t="n">
-        <v>5.41</v>
+        <v>5.88</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1719,6 +1769,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1728,27 +1780,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ITALY 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Inter x AC Monza</t>
+          <t>Sport Huancayo x Cesar Vallejo Moquegua</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Sport Huancayo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Cesar Vallejo Moquegua</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1767,20 +1819,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="L17" t="n">
-        <v>12.82</v>
+        <v>21.28</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1798,6 +1850,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,37 +1861,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al-Masry x Smouha</t>
+          <t>Udinese x Como</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smouha</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1846,20 +1900,20 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1877,6 +1931,8 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1886,27 +1942,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>ITALY 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AEK Athens x Iraklis</t>
+          <t>Inter x AC Monza</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iraklis</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1925,20 +1981,20 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="L19" t="n">
-        <v>16.13</v>
+        <v>12.82</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1956,6 +2012,8 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1965,37 +2023,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CZECH 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Slavia Prague x Bohemians 1905</t>
+          <t>Al-Masry x Smouha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Prague</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Smouha</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2004,20 +2062,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="L20" t="n">
-        <v>18.52</v>
+        <v>5.56</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2035,6 +2093,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2044,27 +2104,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al Ahli x Abha</t>
+          <t>AEK Athens x Iraklis</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Iraklis</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2083,13 +2143,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="K21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="L21" t="n">
-        <v>14.71</v>
+        <v>16.13</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -2114,6 +2174,8 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2123,27 +2185,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>CZECH 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia x Spartak Varna</t>
+          <t>Slavia Prague x Bohemians 1905</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Slavia Prague</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2162,20 +2224,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K22" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="L22" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,6 +2255,8 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2202,27 +2266,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GREECE 1</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Olympiakos x Atromitos</t>
+          <t>Al Ahli x Abha</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2241,20 +2305,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="K23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="L23" t="n">
-        <v>16.67</v>
+        <v>14.71</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2272,6 +2336,8 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2281,37 +2347,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TURKEY 1</t>
+          <t>FRANCE 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fenerbahce x Konyaspor</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fenerbahce</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Konyaspor</t>
-        </is>
-      </c>
+          <t>St Etienne x Grenoble</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2320,37 +2378,45 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="K24" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="L24" t="n">
-        <v>17.86</v>
+        <v>9.52</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2360,37 +2426,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FRANCE 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Toulouse x Lyon</t>
+          <t>PFC Levski Sofia x Spartak Varna</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2399,20 +2465,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="L25" t="n">
-        <v>6.67</v>
+        <v>19.23</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2430,6 +2496,8 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2439,37 +2507,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ITALY 2</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Benevento x Modena</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Benevento</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Modena</t>
-        </is>
-      </c>
+          <t>Levski Sofia x Spartak Varna</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2478,37 +2538,45 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="L26" t="n">
-        <v>6.45</v>
+        <v>7.69</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2518,27 +2586,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ECUADOR 1</t>
+          <t>GREECE 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu) x Manta FC</t>
+          <t>Olympiakos x Atromitos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2557,20 +2625,20 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="L27" t="n">
-        <v>19.23</v>
+        <v>16.67</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2588,6 +2656,8 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2597,27 +2667,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>TURKEY 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sporting Lisbon x Alverca</t>
+          <t>Fenerbahce x Konyaspor</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2636,20 +2706,20 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="K28" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="L28" t="n">
-        <v>13.89</v>
+        <v>17.86</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2667,6 +2737,8 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2676,37 +2748,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Espanyol x Real Madrid</t>
+          <t>Toulouse x Lyon</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2715,20 +2787,20 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>13.16</v>
+        <v>6.67</v>
       </c>
       <c r="M29" t="n">
         <v>100</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2746,6 +2818,8 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2755,37 +2829,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ITALY 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rayo Zuliano x Deportivo La Guaira</t>
+          <t>Benevento x Modena</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2794,20 +2868,20 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="K30" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>16.67</v>
+        <v>6.45</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2825,6 +2899,8 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2834,27 +2910,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>ECUADOR 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Inter Miami CF x Toronto FC</t>
+          <t>Univ Catolica (Ecu) x Manta FC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Toronto FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2873,20 +2949,20 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="K31" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="L31" t="n">
-        <v>17.86</v>
+        <v>19.23</v>
       </c>
       <c r="M31" t="n">
         <v>100</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2904,6 +2980,8 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2913,37 +2991,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>ARGENTINA 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ind Medellin x Cucuta Deportivo</t>
+          <t>Gimnasia La Plata x Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2952,20 +3030,20 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="K32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>17.24</v>
+        <v>9.52</v>
       </c>
       <c r="M32" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2980,9 +3058,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>9.19</v>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2992,27 +3078,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps x FC Dallas</t>
+          <t>Sporting Lisbon x Alverca</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3031,20 +3117,20 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="L33" t="n">
-        <v>20.83</v>
+        <v>13.89</v>
       </c>
       <c r="M33" t="n">
         <v>100</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3062,6 +3148,8 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3071,29 +3159,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Levski Sofia x Spartak Varna</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>Espanyol x Real Madrid</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3102,43 +3198,39 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="K34" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="L34" t="n">
-        <v>7.69</v>
+        <v>13.16</v>
       </c>
       <c r="M34" t="n">
         <v>100</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3148,29 +3240,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FRANCE 2</t>
+          <t>VENEZUELA 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>St Etienne x Grenoble</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Rayo Zuliano x Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Rayo Zuliano</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3179,43 +3279,282 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="L35" t="n">
-        <v>9.52</v>
+        <v>16.67</v>
       </c>
       <c r="M35" t="n">
         <v>100</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Inter Miami CF x Toronto FC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="M36" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ind Medellin x Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="M37" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0x1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps x FC Dallas</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="M38" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5x0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,12 +692,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0x7</t>
+          <t>0-7</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x5</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3x3</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5x1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1x4</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,12 +692,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0-7</t>
+          <t>0x7</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>1x5</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3x3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5x1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1x4</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-22.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,19 +605,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1502,19 +1502,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -3043,19 +3043,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S32" t="n">
